--- a/results/광명금속/광명금속_valid_hybrid_CNN_with_Transformer_(36,32)_first_window.xlsx
+++ b/results/광명금속/광명금속_valid_hybrid_CNN_with_Transformer_(36,32)_first_window.xlsx
@@ -462,10 +462,10 @@
         <v>30.54</v>
       </c>
       <c r="C2" t="n">
-        <v>30.53999900817871</v>
+        <v>30.53999710083008</v>
       </c>
       <c r="D2" t="n">
-        <v>4.982133865356445</v>
+        <v>4.819879055023193</v>
       </c>
     </row>
     <row r="3">
@@ -476,10 +476,10 @@
         <v>31.44</v>
       </c>
       <c r="C3" t="n">
-        <v>31.44000053405762</v>
+        <v>31.44000244140625</v>
       </c>
       <c r="D3" t="n">
-        <v>6.965312480926514</v>
+        <v>7.023138999938965</v>
       </c>
     </row>
     <row r="4">
@@ -490,10 +490,10 @@
         <v>29.18</v>
       </c>
       <c r="C4" t="n">
-        <v>29.18000030517578</v>
+        <v>29.17999649047852</v>
       </c>
       <c r="D4" t="n">
-        <v>8.73198127746582</v>
+        <v>8.378354072570801</v>
       </c>
     </row>
     <row r="5">
@@ -507,7 +507,7 @@
         <v>26.52000045776367</v>
       </c>
       <c r="D5" t="n">
-        <v>10.40187168121338</v>
+        <v>10.0013484954834</v>
       </c>
     </row>
     <row r="6">
@@ -518,10 +518,10 @@
         <v>26.72</v>
       </c>
       <c r="C6" t="n">
-        <v>26.72000122070312</v>
+        <v>26.71999549865723</v>
       </c>
       <c r="D6" t="n">
-        <v>12.02111339569092</v>
+        <v>11.56815910339355</v>
       </c>
     </row>
     <row r="7">
@@ -532,10 +532,10 @@
         <v>26.58</v>
       </c>
       <c r="C7" t="n">
-        <v>26.57999992370605</v>
+        <v>26.57999610900879</v>
       </c>
       <c r="D7" t="n">
-        <v>13.5764684677124</v>
+        <v>12.72249507904053</v>
       </c>
     </row>
     <row r="8">
@@ -546,10 +546,10 @@
         <v>30.44</v>
       </c>
       <c r="C8" t="n">
-        <v>30.44000053405762</v>
+        <v>30.44000244140625</v>
       </c>
       <c r="D8" t="n">
-        <v>14.9852123260498</v>
+        <v>13.80405330657959</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         <v>31.97999954223633</v>
       </c>
       <c r="D9" t="n">
-        <v>16.22962760925293</v>
+        <v>15.1372127532959</v>
       </c>
     </row>
     <row r="10">
@@ -577,7 +577,7 @@
         <v>33.56000137329102</v>
       </c>
       <c r="D10" t="n">
-        <v>17.39617156982422</v>
+        <v>16.37627220153809</v>
       </c>
     </row>
     <row r="11">
@@ -591,7 +591,7 @@
         <v>32.43999862670898</v>
       </c>
       <c r="D11" t="n">
-        <v>18.68571853637695</v>
+        <v>17.65619850158691</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         <v>33.62</v>
       </c>
       <c r="C12" t="n">
-        <v>33.61999893188477</v>
+        <v>33.6199951171875</v>
       </c>
       <c r="D12" t="n">
-        <v>20.30765342712402</v>
+        <v>19.06358337402344</v>
       </c>
     </row>
     <row r="13">
@@ -619,7 +619,7 @@
         <v>30.93999862670898</v>
       </c>
       <c r="D13" t="n">
-        <v>22.24748039245605</v>
+        <v>20.03341293334961</v>
       </c>
     </row>
     <row r="14">
@@ -630,10 +630,10 @@
         <v>25.62</v>
       </c>
       <c r="C14" t="n">
-        <v>25.61999893188477</v>
+        <v>25.61999702453613</v>
       </c>
       <c r="D14" t="n">
-        <v>24.15597534179688</v>
+        <v>20.51610374450684</v>
       </c>
     </row>
     <row r="15">
@@ -647,7 +647,7 @@
         <v>6.139999866485596</v>
       </c>
       <c r="D15" t="n">
-        <v>25.79098701477051</v>
+        <v>21.05801200866699</v>
       </c>
     </row>
     <row r="16">
@@ -661,7 +661,7 @@
         <v>5.519999980926514</v>
       </c>
       <c r="D16" t="n">
-        <v>27.06253623962402</v>
+        <v>21.98143577575684</v>
       </c>
     </row>
     <row r="17">
@@ -675,7 +675,7 @@
         <v>5.659999847412109</v>
       </c>
       <c r="D17" t="n">
-        <v>27.9036808013916</v>
+        <v>22.82674789428711</v>
       </c>
     </row>
     <row r="18">
@@ -689,7 +689,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D18" t="n">
-        <v>28.33634948730469</v>
+        <v>23.18082618713379</v>
       </c>
     </row>
     <row r="19">
@@ -700,10 +700,10 @@
         <v>23.66</v>
       </c>
       <c r="C19" t="n">
-        <v>23.65999984741211</v>
+        <v>23.65999603271484</v>
       </c>
       <c r="D19" t="n">
-        <v>28.44675445556641</v>
+        <v>23.27292060852051</v>
       </c>
     </row>
     <row r="20">
@@ -717,7 +717,7 @@
         <v>24.47999954223633</v>
       </c>
       <c r="D20" t="n">
-        <v>28.24789619445801</v>
+        <v>23.43155860900879</v>
       </c>
     </row>
     <row r="21">
@@ -728,10 +728,10 @@
         <v>25.3</v>
       </c>
       <c r="C21" t="n">
-        <v>25.30000114440918</v>
+        <v>25.29999923706055</v>
       </c>
       <c r="D21" t="n">
-        <v>27.68347930908203</v>
+        <v>23.61184310913086</v>
       </c>
     </row>
     <row r="22">
@@ -742,10 +742,10 @@
         <v>25.06</v>
       </c>
       <c r="C22" t="n">
-        <v>25.05999946594238</v>
+        <v>25.05999755859375</v>
       </c>
       <c r="D22" t="n">
-        <v>26.87213134765625</v>
+        <v>23.86965942382812</v>
       </c>
     </row>
     <row r="23">
@@ -756,10 +756,10 @@
         <v>32.52</v>
       </c>
       <c r="C23" t="n">
-        <v>32.52000045776367</v>
+        <v>32.51999664306641</v>
       </c>
       <c r="D23" t="n">
-        <v>25.95180511474609</v>
+        <v>24.45105743408203</v>
       </c>
     </row>
     <row r="24">
@@ -770,10 +770,10 @@
         <v>26.24</v>
       </c>
       <c r="C24" t="n">
-        <v>26.23999977111816</v>
+        <v>26.2399959564209</v>
       </c>
       <c r="D24" t="n">
-        <v>24.92462539672852</v>
+        <v>24.89355850219727</v>
       </c>
     </row>
     <row r="25">
@@ -784,10 +784,10 @@
         <v>25.66</v>
       </c>
       <c r="C25" t="n">
-        <v>25.65999984741211</v>
+        <v>25.65999794006348</v>
       </c>
       <c r="D25" t="n">
-        <v>23.81265640258789</v>
+        <v>24.6728515625</v>
       </c>
     </row>
     <row r="26">
@@ -801,7 +801,7 @@
         <v>21.05999946594238</v>
       </c>
       <c r="D26" t="n">
-        <v>22.6585521697998</v>
+        <v>24.2343807220459</v>
       </c>
     </row>
     <row r="27">
@@ -812,10 +812,10 @@
         <v>18.38</v>
       </c>
       <c r="C27" t="n">
-        <v>18.3799991607666</v>
+        <v>18.37999725341797</v>
       </c>
       <c r="D27" t="n">
-        <v>21.46502304077148</v>
+        <v>23.58975982666016</v>
       </c>
     </row>
     <row r="28">
@@ -829,7 +829,7 @@
         <v>18.11999893188477</v>
       </c>
       <c r="D28" t="n">
-        <v>20.13141632080078</v>
+        <v>22.45713043212891</v>
       </c>
     </row>
     <row r="29">
@@ -840,10 +840,10 @@
         <v>18.6</v>
       </c>
       <c r="C29" t="n">
-        <v>18.60000038146973</v>
+        <v>18.59999656677246</v>
       </c>
       <c r="D29" t="n">
-        <v>18.53744506835938</v>
+        <v>21.39261627197266</v>
       </c>
     </row>
     <row r="30">
@@ -857,7 +857,7 @@
         <v>18.11999893188477</v>
       </c>
       <c r="D30" t="n">
-        <v>16.71243286132812</v>
+        <v>20.31979179382324</v>
       </c>
     </row>
     <row r="31">
@@ -868,10 +868,10 @@
         <v>18.32</v>
       </c>
       <c r="C31" t="n">
-        <v>18.31999969482422</v>
+        <v>18.32000160217285</v>
       </c>
       <c r="D31" t="n">
-        <v>14.64209461212158</v>
+        <v>19.07406616210938</v>
       </c>
     </row>
     <row r="32">
@@ -882,10 +882,10 @@
         <v>18.42</v>
       </c>
       <c r="C32" t="n">
-        <v>18.42000007629395</v>
+        <v>18.41999816894531</v>
       </c>
       <c r="D32" t="n">
-        <v>12.49913883209229</v>
+        <v>18.32152938842773</v>
       </c>
     </row>
     <row r="33">
@@ -899,7 +899,7 @@
         <v>21.13999938964844</v>
       </c>
       <c r="D33" t="n">
-        <v>11.00299453735352</v>
+        <v>19.54292297363281</v>
       </c>
     </row>
   </sheetData>
